--- a/artfynd/A 53295-2021 artfynd.xlsx
+++ b/artfynd/A 53295-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53295-2021 artfynd.xlsx
+++ b/artfynd/A 53295-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98570400</v>
+        <v>98626518</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554891.234446942</v>
+        <v>554870</v>
       </c>
       <c r="R2" t="n">
-        <v>6365860.963139179</v>
+        <v>6365735</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,52 +774,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98626603</v>
+        <v>98570400</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554843.901922395</v>
+        <v>554891</v>
       </c>
       <c r="R3" t="n">
-        <v>6365770.415802544</v>
+        <v>6365860</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,22 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,6 +869,204 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>98626424</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>554894</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6365752</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Målilla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98626603</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>554844</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6365770</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Målilla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53295-2021 artfynd.xlsx
+++ b/artfynd/A 53295-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98626518</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98570400</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98626424</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,8 +1087,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98626603</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>